--- a/untranslated/downloads/data-excel/9.c.1.xlsx
+++ b/untranslated/downloads/data-excel/9.c.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="195" yWindow="600" windowWidth="28605" windowHeight="15600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -498,13 +498,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -515,7 +515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -533,7 +533,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:15" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -549,8 +549,9 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -596,8 +597,11 @@
       <c r="O4" s="4">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
@@ -643,8 +647,11 @@
       <c r="O5" s="10">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="10">
+        <v>99.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
@@ -690,8 +697,11 @@
       <c r="O6" s="10">
         <v>98.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
@@ -737,8 +747,11 @@
       <c r="O7" s="12">
         <v>98.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="12">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>15</v>
       </c>
@@ -756,7 +769,7 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -768,7 +781,7 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -780,7 +793,7 @@
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -792,7 +805,7 @@
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -804,7 +817,7 @@
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -816,7 +829,7 @@
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -828,7 +841,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -840,7 +853,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
